--- a/Team-Data/2014-15/4-6-2014-15.xlsx
+++ b/Team-Data/2014-15/4-6-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>5.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -784,7 +851,7 @@
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT2" t="n">
         <v>28</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -924,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="AE3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="n">
         <v>18</v>
@@ -936,7 +1003,7 @@
         <v>7</v>
       </c>
       <c r="AI3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ3" t="n">
         <v>1</v>
@@ -969,7 +1036,7 @@
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
         <v>5</v>
@@ -984,7 +1051,7 @@
         <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ3" t="n">
         <v>22</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -1025,25 +1092,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
         <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>0.468</v>
+        <v>0.461</v>
       </c>
       <c r="H4" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I4" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J4" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K4" t="n">
         <v>0.452</v>
@@ -1052,10 +1119,10 @@
         <v>6.6</v>
       </c>
       <c r="M4" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N4" t="n">
-        <v>0.331</v>
+        <v>0.33</v>
       </c>
       <c r="O4" t="n">
         <v>16.5</v>
@@ -1064,7 +1131,7 @@
         <v>22.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.748</v>
+        <v>0.747</v>
       </c>
       <c r="R4" t="n">
         <v>10.2</v>
@@ -1076,10 +1143,10 @@
         <v>42.2</v>
       </c>
       <c r="U4" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V4" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W4" t="n">
         <v>7</v>
@@ -1091,19 +1158,19 @@
         <v>4.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA4" t="n">
         <v>20</v>
       </c>
       <c r="AB4" t="n">
-        <v>98.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3</v>
+        <v>-3.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
         <v>17</v>
@@ -1115,13 +1182,13 @@
         <v>17</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
         <v>15</v>
@@ -1148,16 +1215,16 @@
         <v>24</v>
       </c>
       <c r="AS4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU4" t="n">
         <v>22</v>
       </c>
-      <c r="AU4" t="n">
-        <v>21</v>
-      </c>
       <c r="AV4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
         <v>24</v>
@@ -1175,7 +1242,7 @@
         <v>17</v>
       </c>
       <c r="BB4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1324,7 +1391,7 @@
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR5" t="n">
         <v>25</v>
@@ -1348,7 +1415,7 @@
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ5" t="n">
         <v>3</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -1473,10 +1540,10 @@
         <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH6" t="n">
         <v>7</v>
@@ -1485,7 +1552,7 @@
         <v>22</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK6" t="n">
         <v>20</v>
@@ -1503,7 +1570,7 @@
         <v>2</v>
       </c>
       <c r="AP6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ6" t="n">
         <v>3</v>
@@ -1512,7 +1579,7 @@
         <v>7</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
         <v>3</v>
@@ -1521,7 +1588,7 @@
         <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -1652,16 +1719,16 @@
         <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>14</v>
@@ -1670,7 +1737,7 @@
         <v>25</v>
       </c>
       <c r="AK7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL7" t="n">
         <v>5</v>
@@ -1679,7 +1746,7 @@
         <v>2</v>
       </c>
       <c r="AN7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO7" t="n">
         <v>7</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E8" t="n">
         <v>46</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>0.605</v>
+        <v>0.597</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
@@ -1771,13 +1838,13 @@
         <v>39.4</v>
       </c>
       <c r="J8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K8" t="n">
         <v>0.461</v>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="M8" t="n">
         <v>25.6</v>
@@ -1789,19 +1856,19 @@
         <v>16.8</v>
       </c>
       <c r="P8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.75</v>
+        <v>0.751</v>
       </c>
       <c r="R8" t="n">
         <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U8" t="n">
         <v>22.4</v>
@@ -1822,7 +1889,7 @@
         <v>20.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AB8" t="n">
         <v>104.6</v>
@@ -1831,7 +1898,7 @@
         <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1846,7 +1913,7 @@
         <v>15</v>
       </c>
       <c r="AI8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ8" t="n">
         <v>9</v>
@@ -1870,13 +1937,13 @@
         <v>17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR8" t="n">
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
         <v>24</v>
@@ -1885,7 +1952,7 @@
         <v>8</v>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW8" t="n">
         <v>8</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -2025,10 +2092,10 @@
         <v>24</v>
       </c>
       <c r="AH9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2274,7 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
@@ -2267,7 +2334,7 @@
         <v>23</v>
       </c>
       <c r="BB10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F12" t="n">
         <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J12" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K12" t="n">
         <v>0.442</v>
@@ -2511,16 +2578,16 @@
         <v>33.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O12" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="P12" t="n">
-        <v>25.1</v>
+        <v>25.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.719</v>
+        <v>0.718</v>
       </c>
       <c r="R12" t="n">
         <v>11.9</v>
@@ -2532,10 +2599,10 @@
         <v>43.7</v>
       </c>
       <c r="U12" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V12" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="W12" t="n">
         <v>9.6</v>
@@ -2547,19 +2614,19 @@
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.6</v>
+        <v>103.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
         <v>3</v>
@@ -2571,7 +2638,7 @@
         <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
         <v>20</v>
@@ -2595,7 +2662,7 @@
         <v>6</v>
       </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
@@ -2607,13 +2674,13 @@
         <v>21</v>
       </c>
       <c r="AT12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU12" t="n">
         <v>9</v>
       </c>
       <c r="AV12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW12" t="n">
         <v>2</v>
@@ -2622,13 +2689,13 @@
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
         <v>5</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2820,7 @@
         <v>20</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI13" t="n">
         <v>25</v>
@@ -2780,7 +2847,7 @@
         <v>19</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
         <v>20</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2993,7 @@
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
         <v>5</v>
@@ -2938,7 +3005,7 @@
         <v>29</v>
       </c>
       <c r="AI14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ14" t="n">
         <v>15</v>
@@ -2959,7 +3026,7 @@
         <v>8</v>
       </c>
       <c r="AP14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ14" t="n">
         <v>28</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E15" t="n">
         <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G15" t="n">
-        <v>0.267</v>
+        <v>0.263</v>
       </c>
       <c r="H15" t="n">
         <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
         <v>85.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N15" t="n">
         <v>0.345</v>
       </c>
       <c r="O15" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="P15" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.74</v>
+        <v>0.741</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T15" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U15" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V15" t="n">
         <v>13.2</v>
@@ -3093,19 +3160,19 @@
         <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>98.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.4</v>
+        <v>-6.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,7 +3187,7 @@
         <v>2</v>
       </c>
       <c r="AI15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ15" t="n">
         <v>8</v>
@@ -3141,7 +3208,7 @@
         <v>13</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
         <v>23</v>
@@ -3153,10 +3220,10 @@
         <v>13</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV15" t="n">
         <v>5</v>
@@ -3171,13 +3238,13 @@
         <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA15" t="n">
         <v>24</v>
       </c>
       <c r="BB15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3357,7 @@
         <v>3</v>
       </c>
       <c r="AE16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF16" t="n">
         <v>4</v>
@@ -3359,7 +3426,7 @@
         <v>15</v>
       </c>
       <c r="BB16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC16" t="n">
         <v>8</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3593,7 @@
         <v>22</v>
       </c>
       <c r="AW17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX17" t="n">
         <v>22</v>
@@ -3538,7 +3605,7 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -3663,10 +3730,10 @@
         <v>16</v>
       </c>
       <c r="AH18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ18" t="n">
         <v>26</v>
@@ -3717,7 +3784,7 @@
         <v>14</v>
       </c>
       <c r="AZ18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA18" t="n">
         <v>18</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-8.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E20" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F20" t="n">
         <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>0.533</v>
+        <v>0.539</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,10 +4022,10 @@
         <v>37.9</v>
       </c>
       <c r="J20" t="n">
-        <v>82.5</v>
+        <v>82.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
         <v>7.2</v>
@@ -3967,25 +4034,25 @@
         <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="O20" t="n">
         <v>16.4</v>
       </c>
       <c r="P20" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.761</v>
+        <v>0.755</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
         <v>32</v>
       </c>
       <c r="T20" t="n">
-        <v>43.3</v>
+        <v>43.6</v>
       </c>
       <c r="U20" t="n">
         <v>22.1</v>
@@ -3997,25 +4064,25 @@
         <v>6.7</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z20" t="n">
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB20" t="n">
         <v>99.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AD20" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AE20" t="n">
         <v>14</v>
@@ -4033,10 +4100,10 @@
         <v>12</v>
       </c>
       <c r="AJ20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL20" t="n">
         <v>19</v>
@@ -4051,19 +4118,19 @@
         <v>21</v>
       </c>
       <c r="AP20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
         <v>10</v>
       </c>
       <c r="AS20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU20" t="n">
         <v>10</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4090,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4276,7 @@
         <v>30</v>
       </c>
       <c r="AH21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI21" t="n">
         <v>28</v>
@@ -4221,7 +4288,7 @@
         <v>28</v>
       </c>
       <c r="AL21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4458,7 @@
         <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
         <v>7</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -4483,40 +4550,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E23" t="n">
         <v>24</v>
       </c>
       <c r="F23" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G23" t="n">
-        <v>0.316</v>
+        <v>0.312</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J23" t="n">
         <v>82.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
         <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O23" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="P23" t="n">
         <v>19.1</v>
@@ -4525,43 +4592,43 @@
         <v>0.73</v>
       </c>
       <c r="R23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U23" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V23" t="n">
         <v>14.9</v>
       </c>
       <c r="W23" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X23" t="n">
         <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="n">
         <v>18</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.7</v>
+        <v>-5.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4579,13 +4646,13 @@
         <v>15</v>
       </c>
       <c r="AJ23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
@@ -4603,10 +4670,10 @@
         <v>25</v>
       </c>
       <c r="AR23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT23" t="n">
         <v>25</v>
@@ -4624,10 +4691,10 @@
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY24" t="n">
         <v>27</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -4946,7 +5013,7 @@
         <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL25" t="n">
         <v>9</v>
@@ -4973,7 +5040,7 @@
         <v>12</v>
       </c>
       <c r="AT25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E26" t="n">
         <v>50</v>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G26" t="n">
-        <v>0.649</v>
+        <v>0.658</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
@@ -5053,19 +5120,19 @@
         <v>0.45</v>
       </c>
       <c r="L26" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="M26" t="n">
         <v>27.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.366</v>
+        <v>0.365</v>
       </c>
       <c r="O26" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P26" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="Q26" t="n">
         <v>0.801</v>
@@ -5074,13 +5141,13 @@
         <v>10.8</v>
       </c>
       <c r="S26" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="T26" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
       <c r="U26" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V26" t="n">
         <v>13.6</v>
@@ -5095,31 +5162,31 @@
         <v>3.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AA26" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB26" t="n">
-        <v>102.8</v>
+        <v>102.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="AE26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG26" t="n">
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI26" t="n">
         <v>8</v>
@@ -5137,7 +5204,7 @@
         <v>3</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4</v>
       </c>
       <c r="AD27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E28" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F28" t="n">
         <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>0.658</v>
+        <v>0.662</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
@@ -5411,49 +5478,49 @@
         <v>38.9</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.464</v>
+        <v>0.465</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="O28" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P28" t="n">
         <v>21.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="R28" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
         <v>33.9</v>
       </c>
       <c r="T28" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U28" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W28" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.4</v>
@@ -5471,7 +5538,7 @@
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5486,7 +5553,7 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ28" t="n">
         <v>12</v>
@@ -5501,22 +5568,22 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
         <v>15</v>
       </c>
       <c r="AP28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
         <v>5</v>
       </c>
       <c r="AR28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
         <v>14</v>
@@ -5528,7 +5595,7 @@
         <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5732,7 @@
         <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI29" t="n">
         <v>10</v>
@@ -5704,10 +5771,10 @@
         <v>26</v>
       </c>
       <c r="AU29" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AV29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW29" t="n">
         <v>18</v>
@@ -5719,7 +5786,7 @@
         <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5905,7 @@
         <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF30" t="n">
         <v>18</v>
@@ -5871,7 +5938,7 @@
         <v>14</v>
       </c>
       <c r="AP30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ30" t="n">
         <v>26</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6129,7 @@
         <v>22</v>
       </c>
       <c r="AS31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT31" t="n">
         <v>10</v>
@@ -6077,22 +6144,22 @@
         <v>20</v>
       </c>
       <c r="AX31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY31" t="n">
         <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA31" t="n">
         <v>21</v>
       </c>
       <c r="BB31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-6-2014-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
     </row>
